--- a/examples/Phytoplankton-Huisman-model/LB-Huisman-conversion.xlsx
+++ b/examples/Phytoplankton-Huisman-model/LB-Huisman-conversion.xlsx
@@ -1,17 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrico/Dropbox/2-Recherche/ch4-project/examples/Phytoplankton-Huisman-model/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDF27A7-B290-FB43-BDAB-29B9EF728695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="140" yWindow="1120" windowWidth="26760" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1 - Conversion from Physi" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1 - Conversion from Physi" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>Conversion from Physical to LB units for Huisman model</t>
   </si>
@@ -111,8 +130,8 @@
   <si>
     <r>
       <rPr>
-        <b val="1"/>
-        <u val="single"/>
+        <b/>
+        <u/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
@@ -121,7 +140,7 @@
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
         <sz val="10"/>
         <color indexed="8"/>
         <rFont val="Helvetica Neue"/>
@@ -157,12 +176,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.0###########E+00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0###########E+00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -174,14 +192,14 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <b val="1"/>
-      <u val="single"/>
+      <b/>
+      <u/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
@@ -577,163 +595,163 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="51">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" fillId="6" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -743,31 +761,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffbdc0bf"/>
-      <rgbColor rgb="ffa5a5a5"/>
-      <rgbColor rgb="ff3f3f3f"/>
-      <rgbColor rgb="ffdbdbdb"/>
-      <rgbColor rgb="ff88f94e"/>
-      <rgbColor rgb="ff60d836"/>
-      <rgbColor rgb="fffae232"/>
-      <rgbColor rgb="fff8ba00"/>
-      <rgbColor rgb="fffe634d"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFBDC0BF"/>
+      <rgbColor rgb="FFA5A5A5"/>
+      <rgbColor rgb="FF3F3F3F"/>
+      <rgbColor rgb="FFDBDBDB"/>
+      <rgbColor rgb="FF88F94E"/>
+      <rgbColor rgb="FF60D836"/>
+      <rgbColor rgb="FFFAE232"/>
+      <rgbColor rgb="FFF8BA00"/>
+      <rgbColor rgb="FFFE634D"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -966,7 +1038,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -985,7 +1057,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1200" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1015,7 +1087,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1041,7 +1113,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1067,7 +1139,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1093,7 +1165,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1119,7 +1191,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1145,7 +1217,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1171,7 +1243,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1197,7 +1269,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1223,7 +1295,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1236,9 +1308,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1255,7 +1333,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1274,7 +1352,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1300,7 +1378,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1326,7 +1404,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1352,7 +1430,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1378,7 +1456,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1404,7 +1482,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1430,7 +1508,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1456,7 +1534,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1482,7 +1560,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1508,7 +1586,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1521,9 +1599,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1537,7 +1621,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1556,7 +1640,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1586,7 +1670,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1612,7 +1696,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1638,7 +1722,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1664,7 +1748,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1690,7 +1774,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1716,7 +1800,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1742,7 +1826,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1768,7 +1852,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1794,7 +1878,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1807,516 +1891,522 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:G31"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:IV31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="34.5625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.3516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.875" style="1" customWidth="1"/>
-    <col min="4" max="7" width="16.3516" style="1" customWidth="1"/>
-    <col min="8" max="256" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="34.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
+    <col min="4" max="256" width="16.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.65" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" ht="20.55" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" t="s" s="4">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+    </row>
+    <row r="2" spans="1:7" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s" s="4">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s" s="4">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" ht="20.05" customHeight="1">
-      <c r="A4" t="s" s="13">
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>30</v>
       </c>
-      <c r="C4" t="s" s="15">
+      <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>1</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" ht="20.05" customHeight="1">
-      <c r="A5" t="s" s="13">
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="19">
         <v>0.4</v>
       </c>
-      <c r="C5" t="s" s="15">
+      <c r="C5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="19"/>
-    </row>
-    <row r="6" ht="20.05" customHeight="1">
-      <c r="A6" t="s" s="13">
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="20">
         <f>B5/B4</f>
-        <v>0.0133333333333333</v>
-      </c>
-      <c r="C6" t="s" s="15">
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>1</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="19"/>
-    </row>
-    <row r="7" ht="20.05" customHeight="1">
-      <c r="A7" t="s" s="22">
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="23">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s" s="24">
+      <c r="B7" s="22">
+        <v>30</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <f>B7/B5</f>
-        <v>50</v>
-      </c>
-      <c r="E7" t="s" s="24">
+        <v>75</v>
+      </c>
+      <c r="E7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="19"/>
-    </row>
-    <row r="8" ht="20.05" customHeight="1">
-      <c r="A8" t="s" s="26">
+      <c r="F7" s="17"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>0.04</v>
       </c>
-      <c r="C8" t="s" s="28">
+      <c r="C8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-    </row>
-    <row r="9" ht="20.05" customHeight="1">
-      <c r="A9" s="30"/>
-      <c r="B9" s="27">
+      <c r="D8" s="28"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="29"/>
+      <c r="B9" s="26">
         <f>B8/3600</f>
-        <v>1.11111111111111e-05</v>
-      </c>
-      <c r="C9" t="s" s="28">
+        <v>1.1111111111111112E-5</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f>B9/B6</f>
-        <v>0.000833333333333335</v>
-      </c>
-      <c r="E9" t="s" s="32">
+        <v>8.3333333333333328E-4</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <f>IF(D9&lt;0.5,1,0)</f>
         <v>1</v>
       </c>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10" ht="20.05" customHeight="1">
-      <c r="A10" t="s" s="22">
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="22">
         <v>0.04</v>
       </c>
-      <c r="C10" t="s" s="24">
+      <c r="C10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="19"/>
-    </row>
-    <row r="11" ht="20.05" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="23">
+      <c r="D10" s="33"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="34"/>
+      <c r="B11" s="22">
         <f>B10/3600</f>
-        <v>1.11111111111111e-05</v>
-      </c>
-      <c r="C11" t="s" s="24">
+        <v>1.1111111111111112E-5</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <f>B11*B4</f>
-        <v>0.000333333333333333</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" ht="20.05" customHeight="1">
-      <c r="A12" t="s" s="26">
+        <v>3.3333333333333338E-4</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>0.01</v>
       </c>
-      <c r="C12" t="s" s="28">
+      <c r="C12" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="19"/>
-    </row>
-    <row r="13" ht="20.05" customHeight="1">
-      <c r="A13" s="30"/>
-      <c r="B13" s="27">
+      <c r="D12" s="28"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="29"/>
+      <c r="B13" s="26">
         <f>B12/3600</f>
-        <v>2.77777777777778e-06</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="31">
+        <v>2.7777777777777779E-6</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="30">
         <f>B13*B4</f>
-        <v>8.33333333333334e-05</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="19"/>
-    </row>
-    <row r="14" ht="20.05" customHeight="1">
-      <c r="A14" t="s" s="22">
+        <v>8.3333333333333344E-5</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="36">
-        <v>1.5e-11</v>
-      </c>
-      <c r="C14" t="s" s="24">
+      <c r="B14" s="35">
+        <v>1.5E-11</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <f>B14/(B5*B5)</f>
-        <v>9.375e-11</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" ht="20.05" customHeight="1">
-      <c r="A15" t="s" s="26">
+        <v>9.3749999999999986E-11</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>0.2</v>
       </c>
-      <c r="C15" t="s" s="28">
+      <c r="C15" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <f>B15*B5</f>
-        <v>0.08</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19"/>
-    </row>
-    <row r="16" ht="20.05" customHeight="1">
-      <c r="A16" t="s" s="22">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B16" s="22">
         <v>350</v>
       </c>
-      <c r="C16" t="s" s="24">
+      <c r="C16" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <f>B16/(B4/(B5*B5))</f>
-        <v>1.86666666666667</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
-    </row>
-    <row r="17" ht="20.05" customHeight="1">
-      <c r="A17" t="s" s="26">
+        <v>1.8666666666666669</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>30</v>
       </c>
-      <c r="C17" t="s" s="28">
+      <c r="C17" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <f>B17/(B4/(B5*B5))</f>
-        <v>0.16</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19"/>
-    </row>
-    <row r="18" ht="20.05" customHeight="1">
-      <c r="A18" t="s" s="22">
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="23">
-        <v>10</v>
-      </c>
-      <c r="C18" t="s" s="24">
+      <c r="B18" s="22">
+        <v>1</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="34"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
-    </row>
-    <row r="19" ht="20.05" customHeight="1">
-      <c r="A19" s="35"/>
-      <c r="B19" s="23">
+      <c r="D18" s="33"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="34"/>
+      <c r="B19" s="22">
         <f>B18*0.0001</f>
-        <v>0.001</v>
-      </c>
-      <c r="C19" t="s" s="24">
+        <v>1E-4</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="24">
         <f>B19/(B5*B5/B4)</f>
-        <v>0.1875</v>
-      </c>
-      <c r="E19" t="s" s="37">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="E19" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="37">
         <f>D19*3+0.5</f>
-        <v>1.0625</v>
-      </c>
-      <c r="G19" s="19"/>
-    </row>
-    <row r="20" ht="20.05" customHeight="1">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="21" ht="20.35" customHeight="1">
-      <c r="A21" t="s" s="41">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="42">
+      <c r="B21" s="41">
         <v>1</v>
       </c>
-      <c r="C21" t="s" s="43">
+      <c r="C21" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="43">
         <f>B21*B5*B5*B5</f>
-        <v>0.064</v>
-      </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="19"/>
-    </row>
-    <row r="22" ht="20.35" customHeight="1">
-      <c r="A22" t="s" s="47">
+        <v>6.4000000000000015E-2</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="17"/>
-    </row>
-    <row r="23" ht="20.05" customHeight="1">
-      <c r="A23" t="s" s="50">
+      <c r="B22" s="47"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="16"/>
+    </row>
+    <row r="23" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <f>D7</f>
-        <v>50</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-    </row>
-    <row r="24" ht="20.05" customHeight="1">
-      <c r="A24" t="s" s="50">
+        <v>75</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+    </row>
+    <row r="24" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <f>F19</f>
-        <v>1.0625</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-    </row>
-    <row r="25" ht="20.05" customHeight="1">
-      <c r="A25" t="s" s="50">
+        <v>0.55625000000000002</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+    </row>
+    <row r="25" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="20">
         <f>D9</f>
-        <v>0.000833333333333335</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-    </row>
-    <row r="26" ht="20.05" customHeight="1">
-      <c r="A26" t="s" s="50">
+        <v>8.3333333333333328E-4</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+    </row>
+    <row r="26" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B26" s="20">
         <f>D13</f>
-        <v>8.33333333333334e-05</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-    </row>
-    <row r="27" ht="20.05" customHeight="1">
-      <c r="A27" t="s" s="50">
+        <v>8.3333333333333344E-5</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+    </row>
+    <row r="27" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <f>D11</f>
-        <v>0.000333333333333333</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-    </row>
-    <row r="28" ht="20.05" customHeight="1">
-      <c r="A28" t="s" s="50">
+        <v>3.3333333333333338E-4</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+    </row>
+    <row r="28" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <f>D17</f>
-        <v>0.16</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-    </row>
-    <row r="29" ht="20.05" customHeight="1">
-      <c r="A29" t="s" s="50">
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+    </row>
+    <row r="29" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="21">
+      <c r="B29" s="20">
         <f>D15</f>
-        <v>0.08</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-    </row>
-    <row r="30" ht="20.05" customHeight="1">
-      <c r="A30" t="s" s="50">
+        <v>8.0000000000000016E-2</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+    </row>
+    <row r="30" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <f>D14</f>
-        <v>9.375e-11</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-    </row>
-    <row r="31" ht="20.05" customHeight="1">
-      <c r="A31" t="s" s="50">
+        <v>9.3749999999999986E-11</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="21">
+      <c r="B31" s="20">
         <f>D16</f>
-        <v>1.86666666666667</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+        <v>1.8666666666666669</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A22" r:id="rId1" location="" tooltip="" display="param.in"/>
+    <hyperlink ref="A22" r:id="rId1" display="param.in" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
